--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T06:51:44+00:00</t>
+    <t>2026-06-25T12:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is currently derived from the APS Observation Alcohol Use profile without introducing any additional constraints or changes. It serves as a prepared extension point so that future adaptations can be made independently if required.</t>
+    <t>This FHIR profile is derived from the APS Observation Alcohol Use profile. Additional fields from the PreNUDGE Observation profile are added.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -488,7 +491,7 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for observation</t>
+    <t>Business Identifier for observation, at least one is assigned by the data provider</t>
   </si>
   <si>
     <t>A unique identifier assigned to this observation.</t>
@@ -507,6 +510,206 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Observation.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Observation.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value, if no other specifications are given, use your website url</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Observation.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Observation.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
     <t>Observation.basedOn</t>
@@ -582,9 +785,6 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
@@ -607,10 +807,6 @@
   </si>
   <si>
     <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Classification of  type of observation</t>
@@ -775,8 +971,8 @@
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiminginstant</t>
+    <t xml:space="preserve">dateTime
+</t>
   </si>
   <si>
     <t>Clinically relevant time/time-period for observation</t>
@@ -791,6 +987,13 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -801,6 +1004,15 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t>The mandatory clinically relevant time for observation</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -810,7 +1022,7 @@
 </t>
   </si>
   <si>
-    <t>Date/Time this version was made available</t>
+    <t>The mandatory date/time this version was made available</t>
   </si>
   <si>
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
@@ -859,11 +1071,11 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
-    <t>Actual result</t>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Set to Quantity (drinks/day), as recommended in Observation Social History - Alcohol Use (IPS)</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -907,9 +1119,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -967,7 +1176,7 @@
 </t>
   </si>
   <si>
-    <t>Comments about the observation</t>
+    <t>Comments about the observation including patient comments have to be possible</t>
   </si>
   <si>
     <t>Comments about the observation or the results.</t>
@@ -1019,7 +1228,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>How it was done</t>
+    <t>Manual if derived from a QuestionnaireResponse; Automated only if a plausible automated source is documented</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>
@@ -1031,10 +1240,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>https://fhir.hl7.at/prenudge/appdata/r4/ValueSet/prenudge-observation-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1078,7 +1284,7 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
+    <t>(Measurement) Devices should be documented when used</t>
   </si>
   <si>
     <t>The device used to generate the observation data.</t>
@@ -1131,29 +1337,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1322,7 +1506,7 @@
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
+    <t>QuestionnaireResponse or other source this smoking status observation was derived from</t>
   </si>
   <si>
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
@@ -1337,7 +1521,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>Component results</t>
+    <t>Components should only be used when multiple values are inseparably connected to a single measurement (e.g., score domains).</t>
   </si>
   <si>
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
@@ -1381,6 +1565,10 @@
   </si>
   <si>
     <t>Observation.component.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
     <t>Actual component result</t>
@@ -1543,6 +1731,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1724,12 +1927,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.40234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1746,16 +1949,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1898,7 +2101,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2018,7 +2221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>92</v>
       </c>
@@ -2138,7 +2341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>100</v>
       </c>
@@ -2256,7 +2459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>106</v>
       </c>
@@ -2376,7 +2579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>112</v>
       </c>
@@ -2496,7 +2699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -2616,7 +2819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>129</v>
       </c>
@@ -2736,7 +2939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>137</v>
       </c>
@@ -2856,7 +3059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -2978,7 +3181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>150</v>
       </c>
@@ -2991,7 +3194,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>82</v>
@@ -3098,7 +3301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -3107,14 +3310,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -3123,21 +3326,19 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3185,49 +3386,49 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3243,19 +3444,19 @@
         <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3293,19 +3494,19 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3317,19 +3518,19 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>21</v>
@@ -3338,12 +3539,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3351,7 +3552,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
@@ -3369,16 +3570,16 @@
         <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3403,13 +3604,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3427,10 +3628,10 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3442,30 +3643,30 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3476,7 +3677,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -3485,22 +3686,22 @@
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3525,13 +3726,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3555,7 +3756,7 @@
         <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3570,28 +3771,28 @@
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3610,19 +3811,19 @@
         <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3635,7 +3836,7 @@
         <v>21</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>21</v>
@@ -3647,13 +3848,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3671,10 +3872,10 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>93</v>
@@ -3686,30 +3887,30 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3717,7 +3918,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>93</v>
@@ -3732,20 +3933,18 @@
         <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3757,7 +3956,7 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -3793,7 +3992,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3808,30 +4007,30 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3842,7 +4041,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3854,17 +4053,15 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3913,13 +4110,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -3934,28 +4131,28 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3974,20 +4171,18 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4035,7 +4230,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4050,41 +4245,41 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4096,19 +4291,17 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -4157,13 +4350,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -4172,41 +4365,41 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4218,16 +4411,16 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4277,13 +4470,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -4292,30 +4485,30 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4323,32 +4516,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4373,13 +4568,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4397,13 +4592,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4412,30 +4607,30 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4446,7 +4641,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4455,22 +4650,22 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4495,13 +4690,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4519,16 +4714,16 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>105</v>
@@ -4537,35 +4732,35 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
@@ -4577,22 +4772,22 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4617,13 +4812,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4641,56 +4836,56 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>136</v>
+        <v>274</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4699,22 +4894,22 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4739,13 +4934,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4763,13 +4958,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4778,30 +4973,30 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4821,23 +5016,21 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4885,7 +5078,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4906,28 +5099,28 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4943,21 +5136,23 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4981,13 +5176,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5005,7 +5200,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5020,38 +5215,38 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
@@ -5063,22 +5258,22 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>307</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5103,31 +5298,29 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>21</v>
+        <v>313</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5142,38 +5335,40 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
@@ -5185,21 +5380,23 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5247,7 +5444,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5262,30 +5459,30 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5293,7 +5490,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>
@@ -5305,19 +5502,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5367,7 +5564,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5385,27 +5582,27 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5425,22 +5622,20 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5489,7 +5684,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5501,33 +5696,33 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5547,19 +5742,23 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5607,7 +5806,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5616,47 +5815,47 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5668,18 +5867,20 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5703,13 +5904,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5727,19 +5928,19 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -5748,10 +5949,10 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5760,16 +5961,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5782,25 +5983,25 @@
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>142</v>
+        <v>362</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>148</v>
+        <v>363</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5825,13 +6026,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5849,7 +6050,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5861,33 +6062,33 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>136</v>
+        <v>368</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5898,10 +6099,10 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5910,16 +6111,20 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5967,16 +6172,16 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6000,7 +6205,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>378</v>
       </c>
@@ -6028,7 +6233,7 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>372</v>
+        <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>379</v>
@@ -6036,7 +6241,9 @@
       <c r="M36" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6061,13 +6268,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6094,7 +6301,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6103,27 +6310,27 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6131,7 +6338,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
@@ -6146,19 +6353,19 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6183,31 +6390,29 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6225,13 +6430,13 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>301</v>
+        <v>395</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6240,12 +6445,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6256,7 +6461,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6268,20 +6473,18 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>397</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6305,37 +6508,37 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6347,27 +6550,27 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>301</v>
+        <v>403</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6381,7 +6584,7 @@
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6390,18 +6593,18 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6449,7 +6652,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6467,27 +6670,27 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6498,7 +6701,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6510,16 +6713,20 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6567,19 +6774,19 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>420</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6588,10 +6795,10 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6600,12 +6807,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6616,7 +6823,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6625,20 +6832,18 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>409</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>410</v>
+        <v>161</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6687,19 +6892,19 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>163</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6708,10 +6913,10 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>414</v>
+        <v>164</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6720,16 +6925,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6745,19 +6950,19 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>140</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
+        <v>166</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>419</v>
+        <v>142</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6807,7 +7012,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>170</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6819,7 +7024,7 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
@@ -6828,10 +7033,10 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>164</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -6840,16 +7045,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6862,25 +7067,25 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>349</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>424</v>
+        <v>142</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>425</v>
+        <v>148</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6929,7 +7134,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6941,7 +7146,7 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -6950,10 +7155,10 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>427</v>
+        <v>136</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -6962,12 +7167,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6990,13 +7195,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>431</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>432</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>433</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7047,7 +7252,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>430</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7056,10 +7261,10 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7068,10 +7273,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>362</v>
+        <v>436</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7080,23 +7285,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -7108,17 +7313,15 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>140</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7167,19 +7370,19 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7188,10 +7391,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>440</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7200,47 +7403,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>142</v>
+        <v>444</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>148</v>
+        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7265,13 +7468,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7289,31 +7492,31 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>136</v>
+        <v>368</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7322,12 +7525,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7335,10 +7538,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7347,22 +7550,22 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>205</v>
+        <v>454</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7387,13 +7590,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>206</v>
+        <v>269</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>207</v>
+        <v>455</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>208</v>
+        <v>456</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7411,13 +7614,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7429,27 +7632,27 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>211</v>
+        <v>449</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7469,22 +7672,20 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>271</v>
+        <v>458</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>275</v>
+        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7533,7 +7734,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7551,27 +7752,27 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>279</v>
+        <v>462</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7594,20 +7795,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7631,13 +7828,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7655,7 +7852,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7664,7 +7861,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7676,10 +7873,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>136</v>
+        <v>435</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>290</v>
+        <v>466</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7688,16 +7885,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7713,23 +7910,21 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>468</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>293</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>294</v>
+        <v>470</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7753,13 +7948,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7777,7 +7972,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7795,27 +7990,27 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>300</v>
+        <v>472</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>301</v>
+        <v>473</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7829,29 +8024,27 @@
         <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7899,7 +8092,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7920,19 +8113,1129 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI58" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AJ58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP60">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI59">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:51:02+00:00</t>
+    <t>2026-06-29T13:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:58:40+00:00</t>
+    <t>2026-06-29T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-alcoholuse-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:49:16+00:00</t>
+    <t>2026-06-29T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
